--- a/data/trans_orig/dukeAFECT-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/dukeAFECT-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media de la escala de apoyo afectivo (Duke)</t>
+          <t>Puntuación media de la escala de apoyo afectivo (Duke) (tasa de respuesta: 99,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,31; 17,72</t>
+          <t>17,29; 17,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,93; 18,32</t>
+          <t>17,95; 18,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,88; 17,33</t>
+          <t>16,88; 17,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,29; 17,8</t>
+          <t>17,29; 17,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,59; 17,11</t>
+          <t>16,61; 17,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,58; 17,98</t>
+          <t>17,57; 17,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,59; 17,01</t>
+          <t>16,59; 17,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,27; 17,61</t>
+          <t>17,27; 17,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,02; 17,36</t>
+          <t>17,03; 17,34</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,82; 18,11</t>
+          <t>17,83; 18,1</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,8; 17,12</t>
+          <t>16,8; 17,11</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,33; 17,66</t>
+          <t>17,34; 17,66</t>
         </is>
       </c>
     </row>
@@ -856,22 +856,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,36; 17,74</t>
+          <t>17,36; 17,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,61; 17,92</t>
+          <t>17,59; 17,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,19; 17,52</t>
+          <t>17,18; 17,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,53; 18,97</t>
+          <t>17,52; 18,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -881,17 +881,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,44; 17,78</t>
+          <t>17,47; 17,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,08; 17,4</t>
+          <t>17,08; 17,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,14; 17,45</t>
+          <t>17,14; 17,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,59; 17,82</t>
+          <t>17,59; 17,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,19; 17,42</t>
+          <t>17,18; 17,42</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,41; 18,46</t>
+          <t>17,39; 18,44</t>
         </is>
       </c>
     </row>
@@ -996,17 +996,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,53; 17,99</t>
+          <t>17,53; 18,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,55; 17,97</t>
+          <t>17,54; 17,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,61; 16,96</t>
+          <t>16,61; 16,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,21; 17,69</t>
+          <t>17,25; 17,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,35; 17,75</t>
+          <t>17,36; 17,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,41; 16,77</t>
+          <t>16,4; 16,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,14; 17,83</t>
+          <t>16,06; 17,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,44; 17,78</t>
+          <t>17,47; 17,81</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,53; 17,81</t>
+          <t>17,52; 17,82</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,43; 17,79</t>
+          <t>16,57; 17,79</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,2; 17,58</t>
+          <t>17,19; 17,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,45; 17,79</t>
+          <t>17,42; 17,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,24; 17,59</t>
+          <t>17,24; 17,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,33; 17,74</t>
+          <t>17,36; 17,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,93; 17,35</t>
+          <t>16,92; 17,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,12; 17,48</t>
+          <t>17,13; 17,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,07; 17,46</t>
+          <t>17,07; 17,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,42; 18,14</t>
+          <t>17,44; 18,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,11; 17,39</t>
+          <t>17,1; 17,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,34; 17,58</t>
+          <t>17,33; 17,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,21; 17,46</t>
+          <t>17,21; 17,48</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,46; 17,9</t>
+          <t>17,45; 17,87</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,43; 17,65</t>
+          <t>17,44; 17,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1286,32 +1286,32 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,1; 17,28</t>
+          <t>17,1; 17,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,57; 18,32</t>
+          <t>17,57; 18,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,07; 17,28</t>
+          <t>17,07; 17,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,45; 17,65</t>
+          <t>17,47; 17,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,93; 17,12</t>
+          <t>16,93; 17,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,97; 17,58</t>
+          <t>16,93; 17,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,04; 17,18</t>
+          <t>17,04; 17,17</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,36; 17,81</t>
+          <t>17,35; 17,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/dukeAFECT-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/dukeAFECT-Habitat-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17,57</t>
+          <t>17,47</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,45</t>
+          <t>17,41</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,5</t>
+          <t>17,44</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,29; 17,72</t>
+          <t>17,29; 17,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,95; 18,31</t>
+          <t>17,95; 18,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,88; 17,34</t>
+          <t>16,88; 17,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,29; 17,84</t>
+          <t>17,2; 17,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,61; 17,13</t>
+          <t>16,61; 17,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,57; 17,97</t>
+          <t>17,57; 17,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,59; 17,05</t>
+          <t>16,57; 17,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,27; 17,62</t>
+          <t>17,22; 17,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,03; 17,34</t>
+          <t>17,03; 17,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,83; 18,1</t>
+          <t>17,83; 18,09</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,8; 17,11</t>
+          <t>16,8; 17,13</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,34; 17,66</t>
+          <t>17,29; 17,6</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18,08</t>
+          <t>17,5</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,27 +823,27 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t>17,21</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>17,4</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>17,69</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
           <t>17,3</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>17,4</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>17,69</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>17,3</t>
-        </is>
-      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,73</t>
+          <t>17,36</t>
         </is>
       </c>
     </row>
@@ -861,57 +861,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,59; 17,93</t>
+          <t>17,6; 17,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,18; 17,51</t>
+          <t>17,19; 17,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,52; 18,96</t>
+          <t>17,29; 17,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,05; 17,46</t>
+          <t>17,04; 17,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,47; 17,79</t>
+          <t>17,44; 17,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,08; 17,39</t>
+          <t>17,09; 17,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,14; 17,47</t>
+          <t>17,04; 17,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,26; 17,54</t>
+          <t>17,27; 17,55</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,59; 17,81</t>
+          <t>17,57; 17,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,18; 17,42</t>
+          <t>17,18; 17,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,39; 18,44</t>
+          <t>17,22; 17,5</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17,75</t>
+          <t>17,6</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,11</t>
+          <t>17,59</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,39</t>
+          <t>17,6</t>
         </is>
       </c>
     </row>
@@ -1001,57 +1001,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,54; 17,98</t>
+          <t>17,55; 17,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,61; 16,97</t>
+          <t>16,63; 17,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,53; 17,95</t>
+          <t>17,37; 17,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,25; 17,72</t>
+          <t>17,23; 17,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,36; 17,76</t>
+          <t>17,35; 17,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,4; 16,79</t>
+          <t>16,39; 16,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,06; 17,82</t>
+          <t>17,38; 17,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,47; 17,81</t>
+          <t>17,45; 17,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,52; 17,82</t>
+          <t>17,53; 17,81</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,56; 16,81</t>
+          <t>16,55; 16,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,57; 17,79</t>
+          <t>17,45; 17,73</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,56</t>
+          <t>17,49</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,65</t>
+          <t>17,4</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,61</t>
+          <t>17,44</t>
         </is>
       </c>
     </row>
@@ -1136,27 +1136,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,19; 17,57</t>
+          <t>17,18; 17,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,42; 17,77</t>
+          <t>17,43; 17,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,24; 17,6</t>
+          <t>17,22; 17,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,36; 17,77</t>
+          <t>17,27; 17,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,92; 17,34</t>
+          <t>16,94; 17,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1166,12 +1166,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,07; 17,45</t>
+          <t>17,05; 17,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,44; 18,16</t>
+          <t>17,2; 17,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,33; 17,57</t>
+          <t>17,33; 17,59</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,21; 17,48</t>
+          <t>17,2; 17,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,45; 17,87</t>
+          <t>17,3; 17,57</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17,78</t>
+          <t>17,51</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17,38</t>
+          <t>17,39</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17,58</t>
+          <t>17,45</t>
         </is>
       </c>
     </row>
@@ -1276,47 +1276,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,44; 17,64</t>
+          <t>17,45; 17,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,71; 17,89</t>
+          <t>17,72; 17,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,1; 17,29</t>
+          <t>17,11; 17,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,57; 18,25</t>
+          <t>17,41; 17,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,07; 17,29</t>
+          <t>17,06; 17,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,47; 17,65</t>
+          <t>17,46; 17,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,93; 17,11</t>
+          <t>16,93; 17,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,93; 17,58</t>
+          <t>17,3; 17,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,28; 17,43</t>
+          <t>17,28; 17,44</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,35; 17,82</t>
+          <t>17,38; 17,52</t>
         </is>
       </c>
     </row>
